--- a/output/topology_excel/9104.xlsx
+++ b/output/topology_excel/9104.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,10 +462,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B2" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -484,10 +484,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -506,10 +506,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B4" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -572,10 +572,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -594,10 +594,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B8" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -616,10 +616,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B9" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -638,10 +638,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B10" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -660,10 +660,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -685,7 +685,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -726,10 +726,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -748,10 +748,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -770,10 +770,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="B16" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -792,10 +792,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B17" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
         <v>1</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>311</v>
+        <v>277</v>
       </c>
       <c r="F18" t="n">
         <v>16</v>
@@ -839,7 +839,7 @@
         <v>1</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -850,10 +850,10 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>83</v>
+        <v>280</v>
       </c>
       <c r="F19" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20">
@@ -861,7 +861,7 @@
         <v>1</v>
       </c>
       <c r="B20" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>278</v>
+        <v>169</v>
       </c>
       <c r="F20" t="n">
         <v>16</v>
@@ -883,7 +883,7 @@
         <v>2</v>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>311</v>
+        <v>279</v>
       </c>
       <c r="F21" t="n">
         <v>16</v>
@@ -905,7 +905,7 @@
         <v>2</v>
       </c>
       <c r="B22" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -916,18 +916,18 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>217</v>
+        <v>171</v>
       </c>
       <c r="F22" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -938,10 +938,10 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>410</v>
+        <v>24</v>
       </c>
       <c r="F23" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -949,7 +949,7 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>83</v>
+        <v>311</v>
       </c>
       <c r="F24" t="n">
         <v>16</v>
@@ -971,7 +971,7 @@
         <v>3</v>
       </c>
       <c r="B25" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="F25" t="n">
         <v>16</v>
@@ -993,7 +993,7 @@
         <v>3</v>
       </c>
       <c r="B26" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>169</v>
+        <v>278</v>
       </c>
       <c r="F26" t="n">
         <v>16</v>
@@ -1037,7 +1037,7 @@
         <v>4</v>
       </c>
       <c r="B28" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>83</v>
+        <v>217</v>
       </c>
       <c r="F28" t="n">
         <v>16</v>
@@ -1056,10 +1056,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B29" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1070,18 +1070,18 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>170</v>
+        <v>410</v>
       </c>
       <c r="F29" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B30" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="F30" t="n">
         <v>16</v>
@@ -1103,7 +1103,7 @@
         <v>5</v>
       </c>
       <c r="B31" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>311</v>
+        <v>92</v>
       </c>
       <c r="F31" t="n">
         <v>16</v>
@@ -1125,7 +1125,7 @@
         <v>5</v>
       </c>
       <c r="B32" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>215</v>
+        <v>169</v>
       </c>
       <c r="F32" t="n">
         <v>16</v>
@@ -1147,7 +1147,7 @@
         <v>6</v>
       </c>
       <c r="B33" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>83</v>
+        <v>311</v>
       </c>
       <c r="F33" t="n">
         <v>16</v>
@@ -1169,7 +1169,7 @@
         <v>6</v>
       </c>
       <c r="B34" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>280</v>
+        <v>83</v>
       </c>
       <c r="F34" t="n">
         <v>16</v>
@@ -1188,10 +1188,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B35" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1202,15 +1202,15 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>294</v>
+        <v>170</v>
       </c>
       <c r="F35" t="n">
-        <v>198</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B36" t="n">
         <v>10</v>
@@ -1224,7 +1224,7 @@
         <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>149</v>
+        <v>91</v>
       </c>
       <c r="F36" t="n">
         <v>16</v>
@@ -1235,7 +1235,7 @@
         <v>7</v>
       </c>
       <c r="B37" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1246,10 +1246,10 @@
         <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>293</v>
+        <v>311</v>
       </c>
       <c r="F37" t="n">
-        <v>166</v>
+        <v>16</v>
       </c>
     </row>
     <row r="38">
@@ -1257,7 +1257,7 @@
         <v>7</v>
       </c>
       <c r="B38" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1268,18 +1268,18 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>638</v>
+        <v>215</v>
       </c>
       <c r="F38" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B39" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1290,10 +1290,10 @@
         <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>244</v>
+        <v>83</v>
       </c>
       <c r="F39" t="n">
-        <v>203</v>
+        <v>16</v>
       </c>
     </row>
     <row r="40">
@@ -1301,7 +1301,7 @@
         <v>8</v>
       </c>
       <c r="B40" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>149</v>
+        <v>280</v>
       </c>
       <c r="F40" t="n">
         <v>16</v>
@@ -1320,10 +1320,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B41" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1334,18 +1334,18 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>296</v>
+        <v>149</v>
       </c>
       <c r="F41" t="n">
-        <v>198</v>
+        <v>16</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B42" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1356,18 +1356,18 @@
         <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>295</v>
+        <v>149</v>
       </c>
       <c r="F42" t="n">
-        <v>166</v>
+        <v>16</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B43" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1378,10 +1378,10 @@
         <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>244</v>
+        <v>92</v>
       </c>
       <c r="F43" t="n">
-        <v>201</v>
+        <v>16</v>
       </c>
     </row>
     <row r="44">
@@ -1389,7 +1389,7 @@
         <v>10</v>
       </c>
       <c r="B44" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>149</v>
       </c>
       <c r="F44" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="45">
@@ -1411,7 +1411,7 @@
         <v>10</v>
       </c>
       <c r="B45" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>92</v>
+        <v>149</v>
       </c>
       <c r="F45" t="n">
         <v>16</v>
@@ -1430,7 +1430,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B46" t="n">
         <v>12</v>
@@ -1444,10 +1444,10 @@
         <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>149</v>
+        <v>91</v>
       </c>
       <c r="F46" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="47">
@@ -1455,7 +1455,7 @@
         <v>11</v>
       </c>
       <c r="B47" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="F47" t="n">
         <v>16</v>
@@ -1474,10 +1474,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B48" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1488,19 +1488,19 @@
         <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="F48" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
+        <v>11</v>
+      </c>
+      <c r="B49" t="n">
         <v>12</v>
       </c>
-      <c r="B49" t="n">
-        <v>16</v>
-      </c>
       <c r="C49" t="inlineStr">
         <is>
           <t>Wall</t>
@@ -1510,18 +1510,18 @@
         <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="F49" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B50" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>91</v>
+        <v>170</v>
       </c>
       <c r="F50" t="n">
         <v>16</v>
@@ -1540,10 +1540,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B51" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1557,7 +1557,447 @@
         <v>150</v>
       </c>
       <c r="F51" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>13</v>
+      </c>
+      <c r="B52" t="n">
+        <v>15</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" t="n">
+        <v>278</v>
+      </c>
+      <c r="F52" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>13</v>
+      </c>
+      <c r="B53" t="n">
+        <v>22</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" t="n">
+        <v>82</v>
+      </c>
+      <c r="F53" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>14</v>
+      </c>
+      <c r="B54" t="n">
+        <v>16</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" t="n">
+        <v>280</v>
+      </c>
+      <c r="F54" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>14</v>
+      </c>
+      <c r="B55" t="n">
+        <v>23</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" t="n">
+        <v>230</v>
+      </c>
+      <c r="F55" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>15</v>
+      </c>
+      <c r="B56" t="n">
+        <v>17</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" t="n">
+        <v>182</v>
+      </c>
+      <c r="F56" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>16</v>
+      </c>
+      <c r="B57" t="n">
+        <v>18</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" t="n">
+        <v>182</v>
+      </c>
+      <c r="F57" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>19</v>
+      </c>
+      <c r="B58" t="n">
+        <v>20</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" t="n">
+        <v>149</v>
+      </c>
+      <c r="F58" t="n">
         <v>24</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>21</v>
+      </c>
+      <c r="B59" t="n">
+        <v>22</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" t="n">
+        <v>122</v>
+      </c>
+      <c r="F59" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>22</v>
+      </c>
+      <c r="B60" t="n">
+        <v>24</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" t="n">
+        <v>228</v>
+      </c>
+      <c r="F60" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>23</v>
+      </c>
+      <c r="B61" t="n">
+        <v>25</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" t="n">
+        <v>230</v>
+      </c>
+      <c r="F61" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>24</v>
+      </c>
+      <c r="B62" t="n">
+        <v>25</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" t="n">
+        <v>357</v>
+      </c>
+      <c r="F62" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>13</v>
+      </c>
+      <c r="B63" t="n">
+        <v>17</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" t="n">
+        <v>132</v>
+      </c>
+      <c r="F63" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>14</v>
+      </c>
+      <c r="B64" t="n">
+        <v>18</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" t="n">
+        <v>133</v>
+      </c>
+      <c r="F64" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>1</v>
+      </c>
+      <c r="B65" t="n">
+        <v>17</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" t="n">
+        <v>217</v>
+      </c>
+      <c r="F65" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>1</v>
+      </c>
+      <c r="B66" t="n">
+        <v>13</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" t="n">
+        <v>50</v>
+      </c>
+      <c r="F66" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>2</v>
+      </c>
+      <c r="B67" t="n">
+        <v>18</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" t="n">
+        <v>215</v>
+      </c>
+      <c r="F67" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>2</v>
+      </c>
+      <c r="B68" t="n">
+        <v>14</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" t="n">
+        <v>53</v>
+      </c>
+      <c r="F68" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>13</v>
+      </c>
+      <c r="B69" t="n">
+        <v>21</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" t="n">
+        <v>122</v>
+      </c>
+      <c r="F69" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>1</v>
+      </c>
+      <c r="B70" t="n">
+        <v>24</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" t="n">
+        <v>561</v>
+      </c>
+      <c r="F70" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>2</v>
+      </c>
+      <c r="B71" t="n">
+        <v>25</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" t="n">
+        <v>562</v>
+      </c>
+      <c r="F71" t="n">
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/9104.xlsx
+++ b/output/topology_excel/9104.xlsx
@@ -451,12 +451,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Length_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Width_1</t>
         </is>
       </c>
     </row>
